--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -19822,14 +19822,14 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
         <v>18464400</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>20700</v>
+        <v>22739</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -19893,12 +19893,12 @@
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J290" s="3" t="inlineStr">
@@ -19908,12 +19908,12 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25905,23 +25905,19 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H381" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I381" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>31979000</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>22600</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -25930,12 +25926,12 @@
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M381" s="3" t="inlineStr">
@@ -25945,7 +25941,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27554,10 +27550,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27565,32 +27585,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28404,10 +28400,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28415,32 +28435,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30210,7 +30206,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30230,7 +30226,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -30296,11 +30292,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30308,7 +30322,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30316,7 +30330,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30325,24 +30339,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30872,20 +30868,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $1846万
-$20,700/呎
-(26年-08月-10日)</t>
+$22,739/呎
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -31740,7 +31736,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31750,7 +31746,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31813,11 +31809,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31825,7 +31838,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31834,23 +31847,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -32051,12 +32047,12 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
+$3198万
+$22,600/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -16215,7 +16215,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16225,12 +16225,12 @@
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25703,7 +25703,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>32318600</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>22840</v>
+        <v>24118</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>31059250</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>21950</v>
+        <v>23179</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -27550,11 +27550,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27562,7 +27579,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27570,23 +27587,6 @@
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28400,11 +28400,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28412,7 +28429,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28420,23 +28437,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29250,10 +29250,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29261,34 +29286,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -30292,29 +30292,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30322,7 +30304,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30330,7 +30312,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30338,6 +30320,24 @@
 (26年-08月-25日)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31029,12 +31029,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31042,7 +31060,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31051,31 +31069,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31083,41 +31115,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31809,10 +31809,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31820,32 +31844,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -32018,9 +32018,9 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3232万
-$22,840/呎
+$24,118/呎
 (26年-09月-01日)</t>
         </is>
       </c>
@@ -32173,9 +32173,9 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3106万
-$21,950/呎
+$23,179/呎
 (26年-09月-01日)</t>
         </is>
       </c>

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1251</v>
+        <v>1186</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
         <v>27396900</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>21900</v>
+        <v>23100</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -19883,23 +19883,19 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>18601000</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>20900</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -19908,12 +19904,12 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
@@ -19923,7 +19919,7 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28070,10 +28066,10 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 1251呎 (3房)
+          <t>C | 1186呎 (3房)
 $2740万
-$21,900/呎
-(26年-08月-10日)</t>
+$23,100/呎
+(26年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -29250,12 +29246,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29263,7 +29277,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29271,24 +29285,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30206,7 +30202,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30216,7 +30212,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30292,11 +30288,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30304,7 +30318,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30312,7 +30326,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30321,24 +30335,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30467,7 +30463,7 @@
           <t>A | 1278呎 (3房)
 $3204万
 $25,068/呎
-(26年-08月-18日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -30868,12 +30864,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-招标单位
--
-(在售)</t>
+$1860万
+$20,900/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31029,11 +31025,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31041,42 +31062,35 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31084,7 +31098,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31092,7 +31106,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31100,24 +31114,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31809,11 +31805,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31821,7 +31834,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31829,23 +31842,6 @@
 (24年-06月-17日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>3100</v>
+        <v>2983</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
@@ -15956,14 +15956,14 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
         <v>106640000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>34400</v>
+        <v>35749</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16215,23 +16215,19 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>81173340</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>33780</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16240,12 +16236,12 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
@@ -16255,7 +16251,7 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16281,7 +16277,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -16290,14 +16286,14 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
         <v>20382200</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>22850</v>
+        <v>25101</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -25105,7 +25101,7 @@
         </is>
       </c>
       <c r="E369" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
@@ -25114,14 +25110,14 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
         <v>33252500</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>23500</v>
+        <v>24815</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -29246,10 +29242,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29257,34 +29278,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30202,7 +30198,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30212,7 +30208,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30262,10 +30258,10 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3100呎 (4+房)
+          <t>B | 2983呎 (4+房)
 $10664万
-$34,400/呎
-(26年-08月-13日)</t>
+$35,749/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30288,29 +30284,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30318,7 +30296,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30326,7 +30304,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30335,6 +30313,24 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+$8117万
+$33,780/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30367,10 +30363,10 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $2038万
-$22,850/呎
-(26年-08月-14日)</t>
+$25,101/呎
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -31025,12 +31021,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31038,7 +31052,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31046,24 +31060,6 @@
 (24年-02月-02日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31805,10 +31801,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31816,32 +31836,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31921,10 +31917,10 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3325万
-$23,500/呎
-(26年-09月-01日)</t>
+$24,815/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -25497,7 +25497,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -25506,14 +25506,14 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
         <v>36400000</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>25724</v>
+        <v>27164</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -25893,7 +25893,7 @@
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
@@ -25902,14 +25902,14 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
         <v>31979000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>22600</v>
+        <v>23865</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -28392,10 +28392,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28403,32 +28427,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29242,12 +29242,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29255,7 +29273,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29263,24 +29281,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30284,11 +30284,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+$8117万
+$33,780/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30296,7 +30314,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30304,7 +30322,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30312,24 +30330,6 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-$8117万
-$33,780/呎
-(26年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31064,10 +31064,42 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31075,41 +31107,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31801,11 +31801,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31813,7 +31830,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31822,23 +31839,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -31979,10 +31979,10 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3640万
-$25,724/呎
-(26年-09月-01日)</t>
+$27,164/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -32013,7 +32013,7 @@
           <t>B | 1340呎 (3房)
 $3232万
 $24,118/呎
-(26年-09月-01日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -32041,10 +32041,10 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3198万
-$22,600/呎
-(26年-09月-04日)</t>
+$23,865/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -16352,14 +16352,14 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
         <v>20915000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>23500</v>
+        <v>25726</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16967,12 +16967,12 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J247" s="3" t="inlineStr">
@@ -16982,12 +16982,12 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J248" s="3" t="inlineStr">
@@ -17052,12 +17052,12 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26887,23 +26887,19 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H396" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I396" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H396" s="5" t="n">
+        <v>30847000</v>
+      </c>
+      <c r="I396" s="5" t="n">
+        <v>21800</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -26912,12 +26908,12 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M396" s="3" t="inlineStr">
@@ -26927,7 +26923,7 @@
       </c>
       <c r="N396" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27542,10 +27538,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27553,32 +27573,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28392,11 +28388,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28404,7 +28417,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28412,23 +28425,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29242,10 +29238,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29253,34 +29274,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30198,7 +30194,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30218,7 +30214,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -30355,10 +30351,10 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 890呎 (2房)
+          <t>C | 813呎 (2房)
 $2092万
-$23,500/呎
-(26年-08月-24日)</t>
+$25,726/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -30415,20 +30411,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31064,11 +31060,29 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31076,7 +31090,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31084,7 +31098,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31092,24 +31106,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31728,7 +31724,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31738,7 +31734,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32194,12 +32190,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
+$3085万
+$21,800/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -26694,7 +26694,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -28388,10 +28388,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28399,32 +28423,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29238,12 +29238,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29251,7 +29269,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29259,24 +29277,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31017,11 +31017,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31029,33 +31054,8 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -32164,7 +32164,7 @@
           <t>B | 1340呎 (3房)
 $3106万
 $23,179/呎
-(26年-09月-01日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>2403</v>
+        <v>2283</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -16220,14 +16220,14 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
         <v>81173340</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>33780</v>
+        <v>35556</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16957,23 +16957,19 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="n">
+        <v>33552000</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -16982,12 +16978,12 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
@@ -16997,7 +16993,7 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17027,23 +17023,19 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>33296200</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>23800</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -17052,12 +17044,12 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
@@ -17067,7 +17059,7 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26883,7 +26875,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -26899,7 +26891,7 @@
         <v>30847000</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>21800</v>
+        <v>23020</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -27472,7 +27464,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27492,7 +27484,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -27538,11 +27530,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27550,7 +27559,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27559,23 +27568,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -28087,12 +28079,12 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28388,11 +28380,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28400,7 +28409,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28408,23 +28417,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30194,7 +30186,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30204,7 +30196,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30280,29 +30272,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-$8117万
-$33,780/呎
-(26年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30310,7 +30284,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30318,7 +30292,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30327,6 +30301,24 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2283呎 (4+房)
+$8117万
+$35,556/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30411,20 +30403,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+$3330万
+$23,800/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
-招标单位
--
-(在售)</t>
+$3355万
+$24,000/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31797,10 +31789,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31808,32 +31824,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -32192,9 +32184,9 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3085万
-$21,800/呎
+$23,020/呎
 (26年-09月-24日)</t>
         </is>
       </c>

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -4183,23 +4183,19 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>27271800</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>21800</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4208,12 +4204,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4223,7 +4219,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16483,7 +16479,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16493,12 +16489,12 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J240" s="3" t="inlineStr">
@@ -16508,12 +16504,12 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
@@ -16523,7 +16519,7 @@
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18301,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18315,12 +18311,12 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J267" s="3" t="inlineStr">
@@ -18330,12 +18326,12 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
@@ -18345,7 +18341,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18375,7 +18371,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -18385,12 +18381,12 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J268" s="3" t="inlineStr">
@@ -18400,12 +18396,12 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
@@ -18415,7 +18411,7 @@
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18573,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -18587,12 +18583,12 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J271" s="3" t="inlineStr">
@@ -18602,12 +18598,12 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
@@ -18617,7 +18613,7 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18643,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -18657,12 +18653,12 @@
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I272" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J272" s="3" t="inlineStr">
@@ -18672,12 +18668,12 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
@@ -18687,7 +18683,7 @@
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18845,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -18859,12 +18855,12 @@
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J275" s="3" t="inlineStr">
@@ -18874,12 +18870,12 @@
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
@@ -18889,7 +18885,7 @@
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18915,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -18929,12 +18925,12 @@
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J276" s="3" t="inlineStr">
@@ -18944,12 +18940,12 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
@@ -18959,7 +18955,7 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19121,7 +19117,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -19131,12 +19127,12 @@
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J279" s="3" t="inlineStr">
@@ -19146,12 +19142,12 @@
       </c>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
@@ -19161,7 +19157,7 @@
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19187,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -19201,12 +19197,12 @@
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J280" s="3" t="inlineStr">
@@ -19216,12 +19212,12 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
@@ -19231,7 +19227,7 @@
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19867,7 +19863,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -19876,14 +19872,14 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
         <v>18601000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>20900</v>
+        <v>22879</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -27464,7 +27460,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27474,7 +27470,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28079,12 +28075,12 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
+$2727万
+$21,800/呎
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -28380,10 +28376,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28391,32 +28411,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29230,10 +29226,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29241,34 +29262,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30186,7 +30182,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30206,7 +30202,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30321,46 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2092万
+$25,726/呎
+(26年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$2038万
+$25,101/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30333,7 +30368,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30341,30 +30376,108 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2092万
-$25,726/呎
-(26年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$2065万
+$25,397/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$2038万
-$25,101/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
+$2014万
+$24,800/呎
+(26年-08月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+$3330万
+$23,800/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+$3355万
+$24,000/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2031万
+$24,981/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1987万
+$24,468/呎
+(26年-08月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (3房)
+$3204万
+$25,068/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2011万
+$24,740/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1962万
+$24,167/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30372,7 +30485,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30380,77 +30493,116 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2065万
-$25,397/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$2003万
+$24,637/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$2014万
-$24,800/呎
-(26年-08月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+$1953万
+$24,058/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
-$3330万
-$23,800/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
-$3355万
-$24,000/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2031万
-$24,981/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$1878万
+$23,098/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1987万
-$24,468/呎
-(26年-08月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1278呎 (3房)
-$3204万
-$25,068/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+$1838万
+$22,630/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1863万
+$22,912/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1829万
+$22,520/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 招标单位
@@ -30458,30 +30610,147 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2011万
-$24,740/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+$1927万
+$23,700/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1962万
-$24,167/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
+$1882万
+$23,177/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1829万
+$22,496/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1797万
+$22,135/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1816万
+$22,332/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1793万
+$22,080/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1798万
+$22,113/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1869万
+$23,014/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30489,7 +30758,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30497,30 +30766,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2003万
-$24,637/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$1860万
+$22,879/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1953万
-$24,058/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+$1860万
+$22,904/呎
+(26年-07月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30528,7 +30797,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30536,30 +30805,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1878万
-$23,098/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$1865万
+$22,934/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1838万
-$22,630/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+$1855万
+$22,849/呎
+(26年-08月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30567,279 +30836,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1863万
-$22,912/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1829万
-$22,520/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1927万
-$23,700/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1882万
-$23,177/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1829万
-$22,496/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1797万
-$22,135/呎
-(26年-06月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1816万
-$22,332/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1793万
-$22,080/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1798万
-$22,113/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1869万
-$23,014/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1860万
-$22,879/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1860万
-$22,904/呎
-(26年-07月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1865万
-$22,934/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1855万
-$22,849/呎
-(26年-08月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1382呎 (3房)
@@ -30850,10 +30846,10 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 890呎 (2房)
+          <t>C | 813呎 (2房)
 $1860万
-$20,900/呎
-(26年-09月-11日)</t>
+$22,879/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31052,10 +31048,42 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31063,41 +31091,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -16479,23 +16479,19 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>35061840</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>25062</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
@@ -16504,12 +16500,12 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
@@ -16519,7 +16515,7 @@
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18301,23 +18297,19 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>33090660</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>23670</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
@@ -18326,12 +18318,12 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
@@ -18341,7 +18333,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26880,7 +26872,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -29226,12 +29218,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29239,7 +29249,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29247,24 +29257,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30182,7 +30174,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30192,7 +30184,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30268,11 +30260,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2283呎 (4+房)
+$8117万
+$35,556/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30280,7 +30290,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30288,7 +30298,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30297,31 +30307,286 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2283呎 (4+房)
-$8117万
-$35,556/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+$3506万
+$25,062/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2092万
+$25,726/呎
+(26年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$2038万
+$25,101/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2065万
+$25,397/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$2014万
+$24,800/呎
+(26年-08月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+$3330万
+$23,800/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+$3355万
+$24,000/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2031万
+$24,981/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1987万
+$24,468/呎
+(26年-08月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (3房)
+$3204万
+$25,068/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2011万
+$24,740/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1962万
+$24,167/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2003万
+$24,637/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1953万
+$24,058/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1878万
+$23,098/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1838万
+$22,630/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$1863万
+$22,912/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1829万
+$22,520/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 招标单位
@@ -30329,285 +30594,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2092万
-$25,726/呎
-(26年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$2038万
-$25,101/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2065万
-$25,397/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$2014万
-$24,800/呎
-(26年-08月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-$3330万
-$23,800/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-$3355万
-$24,000/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2031万
-$24,981/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1987万
-$24,468/呎
-(26年-08月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1278呎 (3房)
-$3204万
-$25,068/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2011万
-$24,740/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1962万
-$24,167/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2003万
-$24,637/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1953万
-$24,058/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1878万
-$23,098/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1838万
-$22,630/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1863万
-$22,912/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1829万
-$22,520/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
-招标单位
--
-(在售)</t>
+$3309万
+$23,670/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31005,12 +30997,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31018,7 +31028,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31027,32 +31037,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31060,7 +31070,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31068,7 +31078,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31076,24 +31086,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31785,11 +31777,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31797,7 +31806,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31806,23 +31815,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -32183,7 +32175,7 @@
           <t>B | 1340呎 (3房)
 $3085万
 $23,020/呎
-(26年-09月-24日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -27267,7 +27267,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -27277,12 +27277,12 @@
       </c>
       <c r="H402" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I402" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J402" s="3" t="inlineStr">
@@ -27292,12 +27292,12 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M402" s="3" t="inlineStr">
@@ -27307,7 +27307,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27337,7 +27337,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -27347,12 +27347,12 @@
       </c>
       <c r="H403" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I403" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J403" s="3" t="inlineStr">
@@ -27362,12 +27362,12 @@
       </c>
       <c r="K403" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L403" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M403" s="3" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27518,10 +27518,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27529,32 +27553,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28368,11 +28368,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28380,7 +28397,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28388,23 +28405,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29218,10 +29218,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29229,34 +29254,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31040,10 +31040,42 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31051,41 +31083,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31704,27 +31704,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -32224,20 +32224,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 1385呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -28368,10 +28368,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28379,32 +28403,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30260,10 +30260,42 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1287呎 (3房)
+$3398万
+$26,402/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2127万
+$26,164/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 811呎 (2房)
+$2083万
+$25,689/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2283呎 (4+房)
 $8117万
@@ -30271,41 +30303,9 @@
 (26年-10月-02日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1287呎 (3房)
-$3398万
-$26,402/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2127万
-$26,164/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 811呎 (2房)
-$2083万
-$25,689/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31777,10 +31777,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31788,32 +31812,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>1398</v>
+        <v>1286</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -16954,14 +16954,14 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
         <v>33552000</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>24000</v>
+        <v>26090</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1399</v>
+        <v>1278</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -17020,14 +17020,14 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
         <v>33296200</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>23800</v>
+        <v>26053</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -18565,23 +18565,19 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="n">
+        <v>32950860</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>23570</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
@@ -18590,12 +18586,12 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
@@ -18605,7 +18601,7 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18635,23 +18631,19 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>32680640</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>23360</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -18660,12 +18652,12 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
@@ -18675,7 +18667,7 @@
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27337,23 +27329,19 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H403" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I403" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H403" s="5" t="n">
+        <v>29916000</v>
+      </c>
+      <c r="I403" s="5" t="n">
+        <v>21600</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
@@ -27362,12 +27350,12 @@
       </c>
       <c r="K403" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M403" s="3" t="inlineStr">
@@ -27377,7 +27365,7 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30174,7 +30162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30184,7 +30172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30260,11 +30248,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2283呎 (4+房)
+$8117万
+$35,556/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1287呎 (3房)
 $3398万
@@ -30272,7 +30278,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30280,7 +30286,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30289,24 +30295,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2283呎 (4+房)
-$8117万
-$35,556/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30393,18 +30381,18 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1399呎 (3房)
+          <t>A | 1278呎 (3房)
 $3330万
-$23,800/呎
-(26年-09月-28日)</t>
+$26,053/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1398呎 (3房)
+          <t>B | 1286呎 (3房)
 $3355万
-$24,000/呎
-(26年-09月-28日)</t>
+$26,090/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -30625,20 +30613,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+$3268万
+$23,360/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
-招标单位
--
-(在售)</t>
+$3295万
+$23,570/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -30997,11 +30985,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31009,33 +31022,8 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31704,7 +31692,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31714,7 +31702,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31777,11 +31765,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31789,7 +31794,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31798,23 +31803,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -32224,12 +32212,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 1385呎 (3房)
-招标单位
--
-(在售)</t>
+$2992万
+$21,600/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">

--- a/web/files/九龙-何文田-傲玟.xlsx
+++ b/web/files/九龙-何文田-傲玟.xlsx
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2357</v>
+        <v>2422</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>77867300</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>33037</v>
+        <v>32150</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>31247100</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>26347</v>
+        <v>24978</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2669</v>
+        <v>2764</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>78774000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>29514</v>
+        <v>28500</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>30024000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>25315</v>
+        <v>24000</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>36175000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>26444</v>
+        <v>25000</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>36125000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>26426</v>
+        <v>25000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>34728000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>25386</v>
+        <v>24000</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>35000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>25604</v>
+        <v>24221</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>34293900</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>25069</v>
+        <v>23700</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>34535500</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>25264</v>
+        <v>23900</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>33248700</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>28034</v>
+        <v>26578</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>37415100</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>27350</v>
+        <v>25857</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>34318700</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>25105</v>
+        <v>23750</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>37342750</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>27297</v>
+        <v>25807</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>34246500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>25052</v>
+        <v>23700</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>32648300</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>27528</v>
+        <v>26098</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>37270380</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>27244</v>
+        <v>25757</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>34174000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>24999</v>
+        <v>23650</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>27527000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>23210</v>
+        <v>22004</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>33400000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>24415</v>
+        <v>23082</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>34174250</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>24999</v>
+        <v>23650</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>28522800</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>24050</v>
+        <v>22800</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>33208600</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>24275</v>
+        <v>22950</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>33957500</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>24841</v>
+        <v>23500</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>28297620</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>23860</v>
+        <v>22620</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>33130000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>24218</v>
+        <v>22896</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>34029750</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>24894</v>
+        <v>23550</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>32702200</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>23905</v>
+        <v>22600</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>41980000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>30710</v>
+        <v>29052</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>27922320</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>23543</v>
+        <v>22320</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>32268100</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>23588</v>
+        <v>22300</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>33740750</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>24682</v>
+        <v>23350</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>28147500</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>23733</v>
+        <v>22500</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>32702200</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>23905</v>
+        <v>22600</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>36650000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>26811</v>
+        <v>25363</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>32051050</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>23429</v>
+        <v>22150</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>33379500</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>24418</v>
+        <v>23100</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>32123400</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>23482</v>
+        <v>22200</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>33300000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>24360</v>
+        <v>23045</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>27396900</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>23100</v>
+        <v>21900</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>32094460</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>23461</v>
+        <v>22180</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>33524000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>24524</v>
+        <v>23200</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>31932400</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>23342</v>
+        <v>22068</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>33235000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>24312</v>
+        <v>23000</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>26896500</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>22678</v>
+        <v>21500</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>31800000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>23246</v>
+        <v>21977</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>36039100</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>26364</v>
+        <v>24941</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>25545420</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>21539</v>
+        <v>20420</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>31544600</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>23059</v>
+        <v>21800</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>36524200</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>26719</v>
+        <v>25276</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>25395300</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>21413</v>
+        <v>20300</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1368</v>
+        <v>1447</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>31328000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>22901</v>
+        <v>21650</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1186</v>
+        <v>1251</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>25270200</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>21307</v>
+        <v>20200</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1352</v>
+        <v>1430</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>30316000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>22423</v>
+        <v>21200</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1367</v>
+        <v>1445</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>31000000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>22677</v>
+        <v>21453</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2334</v>
+        <v>2398</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>77000000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>32991</v>
+        <v>32110</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3461</v>
+        <v>3549</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>120666000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>34864</v>
+        <v>34000</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>26124000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>22139</v>
+        <v>21000</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1351</v>
+        <v>1429</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>36296600</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>26866</v>
+        <v>25400</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2338</v>
+        <v>2413</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>76000000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>32506</v>
+        <v>31496</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>26621600</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>22561</v>
+        <v>21400</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>35482500</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>26342</v>
+        <v>24900</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>34934700</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>26366</v>
+        <v>24900</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>27000000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>22881</v>
+        <v>21704</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>34912500</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>25919</v>
+        <v>24500</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>34794400</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>26260</v>
+        <v>24800</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>26124000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>22139</v>
+        <v>21000</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>29947920</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>25380</v>
+        <v>24074</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>33487500</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>24861</v>
+        <v>23500</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>32269000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>24354</v>
+        <v>23000</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>27492400</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>23299</v>
+        <v>22100</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>30843600</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>26139</v>
+        <v>24794</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>32062500</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>23803</v>
+        <v>22500</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>26076700</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>22099</v>
+        <v>20962</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>26920160</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>22814</v>
+        <v>21640</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>31635000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>23486</v>
+        <v>22200</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>25800000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>21864</v>
+        <v>20740</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>31635000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>23486</v>
+        <v>22200</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>31146600</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>23507</v>
+        <v>22200</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>25315400</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>21454</v>
+        <v>20350</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>24880000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>21085</v>
+        <v>20000</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>24148000</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>20464</v>
+        <v>19412</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>29080000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>21947</v>
+        <v>20727</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>24272400</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>20570</v>
+        <v>19512</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>28675000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>21642</v>
+        <v>20438</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>21396800</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>18133</v>
+        <v>17200</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>41846200</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>31066</v>
+        <v>29366</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>27779400</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>20966</v>
+        <v>19800</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>21396800</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>18133</v>
+        <v>17200</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>21322160</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>18070</v>
+        <v>17140</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>21309720</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>18059</v>
+        <v>17130</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>39338717</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>29690</v>
+        <v>28039</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>21297280</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>18049</v>
+        <v>17120</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>21284840</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>18038</v>
+        <v>17110</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>1180</v>
+        <v>1244</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>21272400</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>18027</v>
+        <v>17100</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>1330</v>
+        <v>1408</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>28000000</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>21053</v>
+        <v>19886</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1325</v>
+        <v>1403</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>28040358</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>21163</v>
+        <v>19986</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1683</v>
+        <v>1778</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>54706400</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>32505</v>
+        <v>30769</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>845</v>
+        <v>939</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>18733050</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>22169</v>
+        <v>19950</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>19840000</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>23479</v>
+        <v>21242</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>3255</v>
+        <v>3383</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>110394000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>33915</v>
+        <v>32632</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>845</v>
+        <v>939</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>18826950</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>22280</v>
+        <v>20050</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>19782120</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>23411</v>
+        <v>21180</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>2065</v>
+        <v>2182</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>62500000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>30266</v>
+        <v>28643</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>845</v>
+        <v>939</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>18610980</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>22025</v>
+        <v>19820</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>19567300</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>23157</v>
+        <v>20950</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>2002</v>
+        <v>2120</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>62540000</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>31239</v>
+        <v>29500</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>18404400</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>21806</v>
+        <v>19600</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>19147000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>22659</v>
+        <v>20500</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>26160000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>22689</v>
+        <v>20845</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>26770400</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>23945</v>
+        <v>21800</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>18216600</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>21584</v>
+        <v>19400</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>19427200</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>22991</v>
+        <v>20800</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>25790250</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>22368</v>
+        <v>20550</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>26500240</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>23703</v>
+        <v>21580</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>18028800</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>21361</v>
+        <v>19200</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>18680000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>22107</v>
+        <v>20000</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>25576900</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>22183</v>
+        <v>20380</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>26100000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>23345</v>
+        <v>21254</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>17841000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>21139</v>
+        <v>19000</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>18400000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>21775</v>
+        <v>19700</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>25351000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>21987</v>
+        <v>20200</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>28919600</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>25867</v>
+        <v>23550</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>17653200</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>20916</v>
+        <v>18800</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>19053600</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>22549</v>
+        <v>20400</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>25351000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>21987</v>
+        <v>20200</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>25600000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>22898</v>
+        <v>20847</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>17277600</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>20471</v>
+        <v>18400</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>18820000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>22272</v>
+        <v>20150</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>28700000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>24892</v>
+        <v>22869</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>25419600</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>22737</v>
+        <v>20700</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>17653200</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>20916</v>
+        <v>18800</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>18726700</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>22162</v>
+        <v>20050</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>24974500</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>21660</v>
+        <v>19900</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>25350000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>22674</v>
+        <v>20643</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>17080000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>20237</v>
+        <v>18190</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>18567920</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>21974</v>
+        <v>19880</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>24911750</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>21606</v>
+        <v>19850</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>25051200</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>22407</v>
+        <v>20400</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>16940000</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>20071</v>
+        <v>18040</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>18399800</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>21775</v>
+        <v>19700</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>24650000</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>21379</v>
+        <v>19641</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>24928400</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>22297</v>
+        <v>20300</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>16902000</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>20026</v>
+        <v>18000</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>18306400</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>21664</v>
+        <v>19600</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>24500000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>21249</v>
+        <v>19522</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>24731920</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>22122</v>
+        <v>20140</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>16620000</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>19692</v>
+        <v>17700</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>18119600</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>21443</v>
+        <v>19400</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>24259150</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>21040</v>
+        <v>19330</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>24560000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>21968</v>
+        <v>20000</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>16573350</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>19637</v>
+        <v>17650</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>18035540</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>21344</v>
+        <v>19310</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>24284250</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>21062</v>
+        <v>19350</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>16526400</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>19581</v>
+        <v>17600</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>18000000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>21302</v>
+        <v>19272</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>24284250</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>21062</v>
+        <v>19350</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>24375800</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>21803</v>
+        <v>19850</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>16479450</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>19525</v>
+        <v>17550</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>23970000</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>20789</v>
+        <v>19100</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>24191600</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>21638</v>
+        <v>19700</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>18213000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>21554</v>
+        <v>19500</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>23840000</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>20676</v>
+        <v>18996</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>16244700</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>19247</v>
+        <v>17300</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>17746000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>21001</v>
+        <v>19000</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>23590000</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>20460</v>
+        <v>18797</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>23946000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>21419</v>
+        <v>19500</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>16197750</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>19192</v>
+        <v>17250</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>17652600</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>20891</v>
+        <v>18900</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>22966500</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>19919</v>
+        <v>18300</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>23675840</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>21177</v>
+        <v>19280</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>16188360</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>19181</v>
+        <v>17240</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>17633920</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>20869</v>
+        <v>18880</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>22966500</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>19919</v>
+        <v>18300</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>23639000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>21144</v>
+        <v>19250</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>16188360</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>19181</v>
+        <v>17240</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>17559200</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>20780</v>
+        <v>18800</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>22903750</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>19864</v>
+        <v>18250</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>23368840</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>20902</v>
+        <v>19030</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>844</v>
+        <v>939</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>16178970</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>19169</v>
+        <v>17230</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>829</v>
+        <v>918</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>17258400</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>20818</v>
+        <v>18800</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>1153</v>
+        <v>1255</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>22841000</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>19810</v>
+        <v>18200</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>1118</v>
+        <v>1228</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>23132000</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>20691</v>
+        <v>18837</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>2983</v>
+        <v>3100</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>106640000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>35749</v>
+        <v>34400</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>811</v>
+        <v>898</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>20833600</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>25689</v>
+        <v>23200</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>21271000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>26164</v>
+        <v>23900</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1287</v>
+        <v>1399</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>33980000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>26402</v>
+        <v>24289</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>2283</v>
+        <v>2403</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>81173340</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>35556</v>
+        <v>33780</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>20382200</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>25101</v>
+        <v>22850</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>20915000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>25726</v>
+        <v>23500</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>20138000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>24800</v>
+        <v>22576</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>20648000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>25397</v>
+        <v>23200</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>19868000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>24468</v>
+        <v>22274</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>20309800</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>24981</v>
+        <v>22820</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>1286</v>
+        <v>1398</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>33552000</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>26090</v>
+        <v>24000</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1278</v>
+        <v>1399</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>33296200</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>26053</v>
+        <v>23800</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>19624000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>24167</v>
+        <v>22000</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>20114000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>24740</v>
+        <v>22600</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>1278</v>
+        <v>1399</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>32037100</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>25068</v>
+        <v>22900</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>19534800</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>24058</v>
+        <v>21900</v>
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>20030000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>24637</v>
+        <v>22506</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>18375200</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>22630</v>
+        <v>20600</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>18779000</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>23098</v>
+        <v>21100</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>18286000</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>22520</v>
+        <v>20500</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>18627700</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>22912</v>
+        <v>20930</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>18820000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>23177</v>
+        <v>21099</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>19268500</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>23700</v>
+        <v>21650</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         </is>
       </c>
       <c r="E269" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>17973800</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>22135</v>
+        <v>20150</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>18289500</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>22496</v>
+        <v>20550</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>17929200</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>22080</v>
+        <v>20100</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>18156000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>22332</v>
+        <v>20400</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="E277" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>18687400</v>
       </c>
       <c r="I277" s="5" t="n">
-        <v>23014</v>
+        <v>20950</v>
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>17978000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>22113</v>
+        <v>20200</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>18598200</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>22904</v>
+        <v>20850</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>18601000</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>22879</v>
+        <v>20900</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>18553600</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>22849</v>
+        <v>20800</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>18645500</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>22934</v>
+        <v>20950</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>812</v>
+        <v>892</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>18464400</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>22739</v>
+        <v>20700</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>813</v>
+        <v>890</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>18601000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>22879</v>
+        <v>20900</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>1595</v>
+        <v>1690</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>47793200</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>29964</v>
+        <v>28280</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>19336600</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>23931</v>
+        <v>21800</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         </is>
       </c>
       <c r="E295" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>19239439</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>23811</v>
+        <v>21913</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>2905</v>
+        <v>3007</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>98700000</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>33976</v>
+        <v>32823</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="E297" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>19159000</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>23712</v>
+        <v>21600</v>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         </is>
       </c>
       <c r="E298" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>19120000</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>23663</v>
+        <v>21777</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         </is>
       </c>
       <c r="E299" s="4" t="n">
-        <v>1264</v>
+        <v>1364</v>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>30212600</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>23902</v>
+        <v>22150</v>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="E300" s="4" t="n">
-        <v>2258</v>
+        <v>2376</v>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>71280000</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>31568</v>
+        <v>30000</v>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="E301" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>19026150</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>23547</v>
+        <v>21450</v>
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="E302" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>18833100</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>23308</v>
+        <v>21450</v>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         </is>
       </c>
       <c r="E303" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>30429000</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>24074</v>
+        <v>22050</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>30674800</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>24230</v>
+        <v>22100</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="E307" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>28911000</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>22873</v>
+        <v>20950</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
       <c r="E308" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>29830000</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>23562</v>
+        <v>21491</v>
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         </is>
       </c>
       <c r="E311" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>27889800</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>22065</v>
+        <v>20210</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>28051480</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>22158</v>
+        <v>20210</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         </is>
       </c>
       <c r="E315" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>28152000</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>22272</v>
+        <v>20400</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         </is>
       </c>
       <c r="E316" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>28315200</v>
       </c>
       <c r="I316" s="5" t="n">
-        <v>22366</v>
+        <v>20400</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>28152000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>22272</v>
+        <v>20400</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="E320" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>28037600</v>
       </c>
       <c r="I320" s="5" t="n">
-        <v>22147</v>
+        <v>20200</v>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="E321" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>17747000</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>21964</v>
+        <v>20008</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>17567000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>21741</v>
+        <v>20008</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         </is>
       </c>
       <c r="E323" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>27255000</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>21562</v>
+        <v>19750</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         </is>
       </c>
       <c r="E324" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>27551800</v>
       </c>
       <c r="I324" s="5" t="n">
-        <v>21763</v>
+        <v>19850</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         </is>
       </c>
       <c r="E325" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>17564374</v>
       </c>
       <c r="I325" s="5" t="n">
-        <v>21738</v>
+        <v>19802</v>
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>27204800</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>21489</v>
+        <v>19600</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         </is>
       </c>
       <c r="E332" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>28853744</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>22791</v>
+        <v>20788</v>
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>17740000</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>21955</v>
+        <v>20000</v>
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>26634000</v>
       </c>
       <c r="I335" s="5" t="n">
-        <v>21071</v>
+        <v>19300</v>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>26788400</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>21160</v>
+        <v>19300</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>17606950</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>21791</v>
+        <v>19850</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>17428300</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>21570</v>
+        <v>19850</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>28391706</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>22462</v>
+        <v>20574</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>17616500</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>21803</v>
+        <v>19861</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>17103440</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>21168</v>
+        <v>19480</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>26772000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>21180</v>
+        <v>19400</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="E350" s="4" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>16770000</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>20755</v>
+        <v>19100</v>
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>27324000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>21617</v>
+        <v>19800</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         </is>
       </c>
       <c r="E352" s="4" t="n">
-        <v>1266</v>
+        <v>1388</v>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>27413000</v>
       </c>
       <c r="I352" s="5" t="n">
-        <v>21653</v>
+        <v>19750</v>
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>15827000</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>21019</v>
+        <v>19000</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>753</v>
+        <v>823</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>15660000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>20797</v>
+        <v>19028</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>24840000</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>19652</v>
+        <v>18000</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>1250</v>
+        <v>1372</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>24833000</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>19866</v>
+        <v>18100</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         </is>
       </c>
       <c r="E358" s="4" t="n">
-        <v>3236</v>
+        <v>3337</v>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>114459000</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>35371</v>
+        <v>34300</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="E359" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>18493000</v>
       </c>
       <c r="I359" s="5" t="n">
-        <v>23558</v>
+        <v>21808</v>
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="E360" s="4" t="n">
-        <v>1352</v>
+        <v>1427</v>
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>36278300</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>26833</v>
+        <v>25423</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>2271</v>
+        <v>2361</v>
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>75079800</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>33060</v>
+        <v>31800</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>18330000</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>23350</v>
+        <v>21616</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="E363" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>35579000</v>
       </c>
       <c r="I363" s="5" t="n">
-        <v>26551</v>
+        <v>25144</v>
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>35262600</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>26694</v>
+        <v>25170</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>17985000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>22911</v>
+        <v>21209</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>31392950</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>23428</v>
+        <v>22186</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>34842300</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>26376</v>
+        <v>24870</v>
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         </is>
       </c>
       <c r="E368" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>17775776</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>22644</v>
+        <v>20962</v>
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         </is>
       </c>
       <c r="E369" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>33252500</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>24815</v>
+        <v>23500</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         </is>
       </c>
       <c r="E370" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>33343800</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>25241</v>
+        <v>23800</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="E371" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>17536640</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>22340</v>
+        <v>20680</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="E372" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>31356200</v>
       </c>
       <c r="I372" s="5" t="n">
-        <v>23400</v>
+        <v>22160</v>
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>31154650</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>23584</v>
+        <v>22237</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         </is>
       </c>
       <c r="E374" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>16180000</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>20611</v>
+        <v>19080</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>36400000</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>27164</v>
+        <v>25724</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         </is>
       </c>
       <c r="E376" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>31102200</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>23544</v>
+        <v>22200</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>15980000</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>20357</v>
+        <v>18844</v>
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>32318600</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>24118</v>
+        <v>22840</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>30822000</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>23332</v>
+        <v>22000</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         </is>
       </c>
       <c r="E380" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>15688000</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>19985</v>
+        <v>18500</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>31979000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>23865</v>
+        <v>22600</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>30500000</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>23089</v>
+        <v>21770</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         </is>
       </c>
       <c r="E383" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>15671040</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>19963</v>
+        <v>18480</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="E384" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>30300000</v>
       </c>
       <c r="I384" s="5" t="n">
-        <v>22612</v>
+        <v>21413</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         </is>
       </c>
       <c r="E385" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>30303630</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>22940</v>
+        <v>21630</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>15433600</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>19661</v>
+        <v>18200</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         </is>
       </c>
       <c r="E387" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>31413000</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>23443</v>
+        <v>22200</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         </is>
       </c>
       <c r="E388" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>35122500</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>26588</v>
+        <v>25070</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         </is>
       </c>
       <c r="E389" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>15391200</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>19607</v>
+        <v>18150</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="E390" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>29898950</v>
       </c>
       <c r="I390" s="5" t="n">
-        <v>22313</v>
+        <v>21130</v>
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         </is>
       </c>
       <c r="E391" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>29883000</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>22621</v>
+        <v>21330</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         </is>
       </c>
       <c r="E392" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>15264000</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>19445</v>
+        <v>18000</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>31059250</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>23179</v>
+        <v>21950</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         </is>
       </c>
       <c r="E394" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>30681900</v>
       </c>
       <c r="I394" s="5" t="n">
-        <v>23226</v>
+        <v>21900</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>1340</v>
+        <v>1415</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>30847000</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>23020</v>
+        <v>21800</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="E397" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>29210850</v>
       </c>
       <c r="I397" s="5" t="n">
-        <v>22113</v>
+        <v>20850</v>
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         </is>
       </c>
       <c r="E398" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>15094400</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>19229</v>
+        <v>17800</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         </is>
       </c>
       <c r="E400" s="4" t="n">
-        <v>1321</v>
+        <v>1401</v>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>29280900</v>
       </c>
       <c r="I400" s="5" t="n">
-        <v>22166</v>
+        <v>20900</v>
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         </is>
       </c>
       <c r="E401" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>15026560</v>
       </c>
       <c r="I401" s="5" t="n">
-        <v>19142</v>
+        <v>17720</v>
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
@@ -27496,9 +27496,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2357呎 (4+房)
+          <t>C | 2422呎 (4+房)
 $7787万
-$33,037/呎
+$32,150/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -27506,11 +27506,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27518,7 +27535,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27527,23 +27544,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -27552,18 +27552,18 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 2669呎 (4+房)
+          <t>A | 2764呎 (4+房)
 $7877万
-$29,514/呎
+$28,500/呎
 (25年-03月-13日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $3125万
-$26,347/呎
+$24,978/呎
 (26年-01月-19日)</t>
         </is>
       </c>
@@ -27576,25 +27576,25 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3612万
-$26,426/呎
+$25,000/呎
 (24年-07月-26日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3618万
-$26,444/呎
+$25,000/呎
 (24年-07月-26日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $3002万
-$25,315/呎
+$24,000/呎
 (26年-06月-04日)</t>
         </is>
       </c>
@@ -27607,17 +27607,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3500万
-$25,604/呎
+$24,221/呎
 (24年-10月-10日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3473万
-$25,386/呎
+$24,000/呎
 (24年-12月-24日)</t>
         </is>
       </c>
@@ -27638,17 +27638,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3454万
-$25,264/呎
+$23,900/呎
 (25年-03月-03日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3429万
-$25,069/呎
+$23,700/呎
 (25年-03月-03日)</t>
         </is>
       </c>
@@ -27669,25 +27669,25 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3432万
-$25,105/呎
+$23,750/呎
 (24年-12月-16日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3742万
-$27,350/呎
+$25,857/呎
 (25年-03月-14日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $3325万
-$28,034/呎
+$26,578/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -27700,17 +27700,17 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3425万
-$25,052/呎
+$23,700/呎
 (24年-12月-06日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3734万
-$27,297/呎
+$25,807/呎
 (25年-03月-14日)</t>
         </is>
       </c>
@@ -27731,25 +27731,25 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3417万
-$24,999/呎
+$23,650/呎
 (24年-12月-16日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3727万
-$27,244/呎
+$25,757/呎
 (25年-04月-23日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $3265万
-$27,528/呎
+$26,098/呎
 (26年-08月-25日)</t>
         </is>
       </c>
@@ -27762,25 +27762,25 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3417万
-$24,999/呎
+$23,650/呎
 (24年-12月-10日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3340万
-$24,415/呎
+$23,082/呎
 (25年-06月-02日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2753万
-$23,210/呎
+$22,004/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -27793,25 +27793,25 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3396万
-$24,841/呎
+$23,500/呎
 (24年-11月-21日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3321万
-$24,275/呎
+$22,950/呎
 (25年-07月-22日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2852万
-$24,050/呎
+$22,800/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -27824,25 +27824,25 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3403万
-$24,894/呎
+$23,550/呎
 (24年-12月-24日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3313万
-$24,218/呎
+$22,896/呎
 (25年-06月-13日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2830万
-$23,860/呎
+$22,620/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -27855,17 +27855,17 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $4198万
-$30,710/呎
+$29,052/呎
 (26年-02月-10日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3270万
-$23,905/呎
+$22,600/呎
 (25年-08月-07日)</t>
         </is>
       </c>
@@ -27886,25 +27886,25 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3374万
-$24,682/呎
+$23,350/呎
 (25年-01月-03日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3227万
-$23,588/呎
+$22,300/呎
 (24年-08月-23日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2792万
-$23,543/呎
+$22,320/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -27917,25 +27917,25 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3665万
-$26,811/呎
+$25,363/呎
 (25年-06月-13日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3270万
-$23,905/呎
+$22,600/呎
 (26年-04月-20日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2815万
-$23,733/呎
+$22,500/呎
 (26年-07月-28日)</t>
         </is>
       </c>
@@ -27948,17 +27948,17 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3338万
-$24,418/呎
+$23,100/呎
 (25年-11月-20日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3205万
-$23,429/呎
+$22,150/呎
 (25年-08月-15日)</t>
         </is>
       </c>
@@ -27979,17 +27979,17 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3330万
-$24,360/呎
+$23,045/呎
 (25年-11月-19日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3212万
-$23,482/呎
+$22,200/呎
 (26年-03月-30日)</t>
         </is>
       </c>
@@ -28010,25 +28010,25 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3352万
-$24,524/呎
+$23,200/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3209万
-$23,461/呎
+$22,180/呎
 (26年-04月-13日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2740万
-$23,100/呎
+$21,900/呎
 (26年-09月-11日)</t>
         </is>
       </c>
@@ -28041,17 +28041,17 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3324万
-$24,312/呎
+$23,000/呎
 (24年-04月-12日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3193万
-$23,342/呎
+$22,068/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -28072,25 +28072,25 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3604万
-$26,364/呎
+$24,941/呎
 (25年-02月-17日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3180万
-$23,246/呎
+$21,977/呎
 (26年-04月-17日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2690万
-$22,678/呎
+$21,500/呎
 (26年-08月-19日)</t>
         </is>
       </c>
@@ -28103,25 +28103,25 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3652万
-$26,719/呎
+$25,276/呎
 (25年-10月-06日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3154万
-$23,059/呎
+$21,800/呎
 (26年-04月-28日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2555万
-$21,539/呎
+$20,420/呎
 (26年-05月-29日)</t>
         </is>
       </c>
@@ -28142,17 +28142,17 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>B | 1368呎 (3房)
+          <t>B | 1447呎 (3房)
 $3133万
-$22,901/呎
+$21,650/呎
 (26年-05月-11日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2540万
-$21,413/呎
+$20,300/呎
 (26年-05月-05日)</t>
         </is>
       </c>
@@ -28165,25 +28165,25 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 1367呎 (3房)
+          <t>A | 1445呎 (3房)
 $3100万
-$22,677/呎
+$21,453/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>B | 1352呎 (3房)
+          <t>B | 1430呎 (3房)
 $3032万
-$22,423/呎
+$21,200/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 1186呎 (3房)
+          <t>C | 1251呎 (3房)
 $2527万
-$21,307/呎
+$20,200/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -28338,17 +28338,17 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3461呎 (4+房)
+          <t>B | 3549呎 (4+房)
 $12067万
-$34,864/呎
+$34,000/呎
 (26年-03月-11日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2334呎 (4+房)
+          <t>C | 2398呎 (4+房)
 $7700万
-$32,991/呎
+$32,110/呎
 (24年-04月-15日)</t>
         </is>
       </c>
@@ -28356,43 +28356,43 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2413呎 (4+房)
+$7600万
+$31,496/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1429呎 (3房)
+$3630万
+$25,400/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 1244呎 (3房)
+$2612万
+$21,000/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28402,25 +28402,25 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $3493万
-$26,366/呎
+$24,900/呎
 (24年-01月-25日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3548万
-$26,342/呎
+$24,900/呎
 (24年-01月-26日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2662万
-$22,561/呎
+$21,400/呎
 (26年-04月-17日)</t>
         </is>
       </c>
@@ -28433,25 +28433,25 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $3479万
-$26,260/呎
+$24,800/呎
 (23年-12月-01日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3491万
-$25,919/呎
+$24,500/呎
 (23年-10月-17日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2700万
-$22,881/呎
+$21,704/呎
 (24年-09月-17日)</t>
         </is>
       </c>
@@ -28480,9 +28480,9 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2612万
-$22,139/呎
+$21,000/呎
 (24年-08月-23日)</t>
         </is>
       </c>
@@ -28495,25 +28495,25 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $3227万
-$24,354/呎
+$23,000/呎
 (24年-02月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3349万
-$24,861/呎
+$23,500/呎
 (23年-11月-30日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2995万
-$25,380/呎
+$24,074/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -28542,9 +28542,9 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2749万
-$23,299/呎
+$22,100/呎
 (26年-07月-10日)</t>
         </is>
       </c>
@@ -28565,17 +28565,17 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3206万
-$23,803/呎
+$22,500/呎
 (23年-12月-12日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $3084万
-$26,139/呎
+$24,794/呎
 (26年-07月-08日)</t>
         </is>
       </c>
@@ -28604,9 +28604,9 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2608万
-$22,099/呎
+$20,962/呎
 (24年-04月-17日)</t>
         </is>
       </c>
@@ -28627,17 +28627,17 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3164万
-$23,486/呎
+$22,200/呎
 (24年-01月-03日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2692万
-$22,814/呎
+$21,640/呎
 (26年-06月-24日)</t>
         </is>
       </c>
@@ -28650,25 +28650,25 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $3115万
-$23,507/呎
+$22,200/呎
 (23年-11月-30日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $3164万
-$23,486/呎
+$22,200/呎
 (24年-08月-05日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2580万
-$21,864/呎
+$20,740/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -28697,9 +28697,9 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2532万
-$21,454/呎
+$20,350/呎
 (24年-03月-06日)</t>
         </is>
       </c>
@@ -28728,9 +28728,9 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2488万
-$21,085/呎
+$20,000/呎
 (24年-01月-29日)</t>
         </is>
       </c>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 -
 -
 (暂停销售)</t>
@@ -28774,9 +28774,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $2908万
-$21,947/呎
+$20,727/呎
 (23年-12月-07日)</t>
         </is>
       </c>
@@ -28790,9 +28790,9 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2415万
-$20,464/呎
+$19,412/呎
 (25年-08月-15日)</t>
         </is>
       </c>
@@ -28805,9 +28805,9 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $2868万
-$21,642/呎
+$20,438/呎
 (23年-12月-06日)</t>
         </is>
       </c>
@@ -28821,9 +28821,9 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2427万
-$20,570/呎
+$19,512/呎
 (25年-08月-15日)</t>
         </is>
       </c>
@@ -28836,25 +28836,25 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $2778万
-$20,966/呎
+$19,800/呎
 (23年-10月-17日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $4185万
-$31,066/呎
+$29,366/呎
 (20年-05月-18日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2140万
-$18,133/呎
+$17,200/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -28883,9 +28883,9 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2140万
-$18,133/呎
+$17,200/呎
 (26年-01月-02日)</t>
         </is>
       </c>
@@ -28914,9 +28914,9 @@
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2132万
-$18,070/呎
+$17,140/呎
 (26年-01月-26日)</t>
         </is>
       </c>
@@ -28929,9 +28929,9 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $3934万
-$29,690/呎
+$28,039/呎
 (20年-05月-18日)</t>
         </is>
       </c>
@@ -28945,9 +28945,9 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2131万
-$18,059/呎
+$17,130/呎
 (26年-03月-30日)</t>
         </is>
       </c>
@@ -28976,9 +28976,9 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2130万
-$18,049/呎
+$17,120/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -29007,9 +29007,9 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2128万
-$18,038/呎
+$17,110/呎
 (26年-05月-14日)</t>
         </is>
       </c>
@@ -29022,25 +29022,25 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 1325呎 (3房)
+          <t>A | 1403呎 (3房)
 $2804万
-$21,163/呎
+$19,986/呎
 (24年-01月-17日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>B | 1330呎 (3房)
+          <t>B | 1408呎 (3房)
 $2800万
-$21,053/呎
+$19,886/呎
 (24年-01月-19日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 1180呎 (3房)
+          <t>C | 1244呎 (3房)
 $2127万
-$18,027/呎
+$17,100/呎
 (26年-05月-14日)</t>
         </is>
       </c>
@@ -29195,9 +29195,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 1683呎 (4+房)
+          <t>C | 1778呎 (4+房)
 $5471万
-$32,505/呎
+$30,769/呎
 (25年-12月-16日)</t>
         </is>
       </c>
@@ -29206,45 +29206,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3383呎 (4+房)
+$11039万
+$32,632/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
       <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 934呎 (2房)
+$1984万
+$21,242/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 939呎 (2房)
+$1873万
+$19,950/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29254,26 +29254,26 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 2065呎 (4+房)
+          <t>A | 2182呎 (4+房)
 $6250万
-$30,266/呎
+$28,643/呎
 (24年-02月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1978万
-$23,411/呎
+$21,180/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 845呎 (2房)
+          <t>D | 939呎 (2房)
 $1883万
-$22,280/呎
+$20,050/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -29286,26 +29286,26 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 2002呎 (4+房)
+          <t>A | 2120呎 (4+房)
 $6254万
-$31,239/呎
+$29,500/呎
 (24年-03月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1957万
-$23,157/呎
+$20,950/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 845呎 (2房)
+          <t>D | 939呎 (2房)
 $1861万
-$22,025/呎
+$19,820/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -29318,33 +29318,33 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2677万
-$23,945/呎
+$21,800/呎
 (26年-03月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2616万
-$22,689/呎
+$20,845/呎
 (24年-10月-15日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1915万
-$22,659/呎
+$20,500/呎
 (24年-08月-30日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1840万
-$21,806/呎
+$19,600/呎
 (26年-05月-18日)</t>
         </is>
       </c>
@@ -29357,33 +29357,33 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2650万
-$23,703/呎
+$21,580/呎
 (26年-03月-11日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2579万
-$22,368/呎
+$20,550/呎
 (24年-11月-19日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1943万
-$22,991/呎
+$20,800/呎
 (26年-02月-12日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1822万
-$21,584/呎
+$19,400/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -29396,33 +29396,33 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2610万
-$23,345/呎
+$21,254/呎
 (25年-11月-07日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2558万
-$22,183/呎
+$20,380/呎
 (25年-08月-25日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1868万
-$22,107/呎
+$20,000/呎
 (25年-06月-02日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1803万
-$21,361/呎
+$19,200/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -29435,33 +29435,33 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2892万
-$25,867/呎
+$23,550/呎
 (25年-09月-02日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2535万
-$21,987/呎
+$20,200/呎
 (25年-08月-27日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1840万
-$21,775/呎
+$19,700/呎
 (25年-08月-15日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1784万
-$21,139/呎
+$19,000/呎
 (26年-05月-20日)</t>
         </is>
       </c>
@@ -29474,33 +29474,33 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2560万
-$22,898/呎
+$20,847/呎
 (25年-10月-28日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2535万
-$21,987/呎
+$20,200/呎
 (25年-12月-24日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1905万
-$22,549/呎
+$20,400/呎
 (26年-04月-15日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1765万
-$20,916/呎
+$18,800/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -29513,33 +29513,33 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2542万
-$22,737/呎
+$20,700/呎
 (26年-01月-05日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2870万
-$24,892/呎
+$22,869/呎
 (25年-12月-23日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1882万
-$22,272/呎
+$20,150/呎
 (26年-03月-30日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1728万
-$20,471/呎
+$18,400/呎
 (26年-03月-13日)</t>
         </is>
       </c>
@@ -29552,33 +29552,33 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2535万
-$22,674/呎
+$20,643/呎
 (26年-02月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2497万
-$21,660/呎
+$19,900/呎
 (26年-01月-07日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1873万
-$22,162/呎
+$20,050/呎
 (26年-03月-16日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1765万
-$20,916/呎
+$18,800/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -29591,33 +29591,33 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2505万
-$22,407/呎
+$20,400/呎
 (25年-10月-31日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2491万
-$21,606/呎
+$19,850/呎
 (25年-05月-02日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1857万
-$21,974/呎
+$19,880/呎
 (26年-04月-08日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1708万
-$20,237/呎
+$18,190/呎
 (24年-12月-19日)</t>
         </is>
       </c>
@@ -29630,33 +29630,33 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2493万
-$22,297/呎
+$20,300/呎
 (25年-07月-28日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2465万
-$21,379/呎
+$19,641/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1840万
-$21,775/呎
+$19,700/呎
 (26年-01月-16日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1694万
-$20,071/呎
+$18,040/呎
 (24年-12月-06日)</t>
         </is>
       </c>
@@ -29669,33 +29669,33 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2473万
-$22,122/呎
+$20,140/呎
 (25年-09月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2450万
-$21,249/呎
+$19,522/呎
 (25年-12月-18日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1831万
-$21,664/呎
+$19,600/呎
 (26年-02月-23日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1690万
-$20,026/呎
+$18,000/呎
 (24年-08月-09日)</t>
         </is>
       </c>
@@ -29708,33 +29708,33 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2456万
-$21,968/呎
+$20,000/呎
 (25年-03月-28日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2426万
-$21,040/呎
+$19,330/呎
 (25年-11月-03日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1812万
-$21,443/呎
+$19,400/呎
 (25年-12月-10日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1662万
-$19,692/呎
+$17,700/呎
 (25年-02月-21日)</t>
         </is>
       </c>
@@ -29755,25 +29755,25 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2428万
-$21,062/呎
+$19,350/呎
 (26年-01月-08日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1804万
-$21,344/呎
+$19,310/呎
 (26年-01月-05日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1657万
-$19,637/呎
+$17,650/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -29786,33 +29786,33 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2438万
-$21,803/呎
+$19,850/呎
 (25年-11月-19日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2428万
-$21,062/呎
+$19,350/呎
 (24年-11月-15日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1800万
-$21,302/呎
+$19,272/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1653万
-$19,581/呎
+$17,600/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -29825,17 +29825,17 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2419万
-$21,638/呎
+$19,700/呎
 (25年-10月-06日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2397万
-$20,789/呎
+$19,100/呎
 (25年-12月-18日)</t>
         </is>
       </c>
@@ -29849,9 +29849,9 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1648万
-$19,525/呎
+$17,550/呎
 (26年-03月-11日)</t>
         </is>
       </c>
@@ -29872,17 +29872,17 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2384万
-$20,676/呎
+$18,996/呎
 (25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1821万
-$21,554/呎
+$19,500/呎
 (20年-05月-08日)</t>
         </is>
       </c>
@@ -29903,33 +29903,33 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2395万
-$21,419/呎
+$19,500/呎
 (24年-10月-24日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2359万
-$20,460/呎
+$18,797/呎
 (25年-12月-18日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1775万
-$21,001/呎
+$19,000/呎
 (24年-04月-26日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1624万
-$19,247/呎
+$17,300/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -29942,33 +29942,33 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2368万
-$21,177/呎
+$19,280/呎
 (25年-01月-06日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2297万
-$19,919/呎
+$18,300/呎
 (25年-10月-17日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1765万
-$20,891/呎
+$18,900/呎
 (26年-01月-16日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1620万
-$19,192/呎
+$17,250/呎
 (26年-03月-27日)</t>
         </is>
       </c>
@@ -29981,33 +29981,33 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2364万
-$21,144/呎
+$19,250/呎
 (24年-10月-28日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2297万
-$19,919/呎
+$18,300/呎
 (26年-01月-19日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1763万
-$20,869/呎
+$18,880/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1619万
-$19,181/呎
+$17,240/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -30020,33 +30020,33 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2337万
-$20,902/呎
+$19,030/呎
 (25年-10月-10日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2290万
-$19,864/呎
+$18,250/呎
 (26年-02月-16日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 845呎 (2房)
+          <t>C | 934呎 (2房)
 $1756万
-$20,780/呎
+$18,800/呎
 (26年-03月-05日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1619万
-$19,181/呎
+$17,240/呎
 (26年-04月-27日)</t>
         </is>
       </c>
@@ -30059,33 +30059,33 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 1118呎 (3房)
+          <t>A | 1228呎 (3房)
 $2313万
-$20,691/呎
+$18,837/呎
 (25年-10月-30日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>B | 1153呎 (3房)
+          <t>B | 1255呎 (3房)
 $2284万
-$19,810/呎
+$18,200/呎
 (26年-04月-02日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>C | 829呎 (2房)
+          <t>C | 918呎 (2房)
 $1726万
-$20,818/呎
+$18,800/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>D | 844呎 (2房)
+          <t>D | 939呎 (2房)
 $1618万
-$19,169/呎
+$17,230/呎
 (26年-04月-27日)</t>
         </is>
       </c>
@@ -30222,9 +30222,9 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 2983呎 (4+房)
+          <t>B | 3100呎 (4+房)
 $10664万
-$35,749/呎
+$34,400/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -30248,52 +30248,52 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2283呎 (4+房)
-$8117万
-$35,556/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1399呎 (3房)
+$3398万
+$24,289/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+$2127万
+$23,900/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 898呎 (2房)
+$2083万
+$23,200/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1287呎 (3房)
-$3398万
-$26,402/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2127万
-$26,164/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 811呎 (2房)
-$2083万
-$25,689/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+$8117万
+$33,780/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30319,17 +30319,17 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $2092万
-$25,726/呎
+$23,500/呎
 (26年-09月-23日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $2038万
-$25,101/呎
+$22,850/呎
 (26年-09月-15日)</t>
         </is>
       </c>
@@ -30358,17 +30358,17 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $2065万
-$25,397/呎
+$23,200/呎
 (26年-07月-27日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $2014万
-$24,800/呎
+$22,576/呎
 (26年-08月-11日)</t>
         </is>
       </c>
@@ -30381,33 +30381,33 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1278呎 (3房)
+          <t>A | 1399呎 (3房)
 $3330万
-$26,053/呎
+$23,800/呎
 (26年-10月-26日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1286呎 (3房)
+          <t>B | 1398呎 (3房)
 $3355万
-$26,090/呎
+$24,000/呎
 (26年-10月-26日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $2031万
-$24,981/呎
+$22,820/呎
 (26年-07月-27日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1987万
-$24,468/呎
+$22,274/呎
 (26年-08月-11日)</t>
         </is>
       </c>
@@ -30420,9 +30420,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1278呎 (3房)
+          <t>A | 1399呎 (3房)
 $3204万
-$25,068/呎
+$22,900/呎
 (26年-09月-11日)</t>
         </is>
       </c>
@@ -30436,17 +30436,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $2011万
-$24,740/呎
+$22,600/呎
 (26年-07月-08日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1962万
-$24,167/呎
+$22,000/呎
 (26年-07月-17日)</t>
         </is>
       </c>
@@ -30475,17 +30475,17 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $2003万
-$24,637/呎
+$22,506/呎
 (26年-07月-03日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1953万
-$24,058/呎
+$21,900/呎
 (26年-07月-10日)</t>
         </is>
       </c>
@@ -30514,17 +30514,17 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1878万
-$23,098/呎
+$21,100/呎
 (26年-05月-28日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1838万
-$22,630/呎
+$20,600/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -30553,17 +30553,17 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1863万
-$22,912/呎
+$20,930/呎
 (26年-05月-26日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1829万
-$22,520/呎
+$20,500/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -30592,17 +30592,17 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1927万
-$23,700/呎
+$21,650/呎
 (26年-06月-30日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1882万
-$23,177/呎
+$21,099/呎
 (26年-07月-02日)</t>
         </is>
       </c>
@@ -30631,17 +30631,17 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1829万
-$22,496/呎
+$20,550/呎
 (26年-05月-27日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1797万
-$22,135/呎
+$20,150/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -30670,17 +30670,17 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1816万
-$22,332/呎
+$20,400/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1793万
-$22,080/呎
+$20,100/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -30709,17 +30709,17 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1798万
-$22,113/呎
+$20,200/呎
 (26年-06月-08日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1869万
-$23,014/呎
+$20,950/呎
 (26年-07月-10日)</t>
         </is>
       </c>
@@ -30748,17 +30748,17 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1860万
-$22,879/呎
+$20,900/呎
 (26年-07月-15日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1860万
-$22,904/呎
+$20,850/呎
 (26年-07月-21日)</t>
         </is>
       </c>
@@ -30787,17 +30787,17 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1865万
-$22,934/呎
+$20,950/呎
 (26年-08月-10日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1855万
-$22,849/呎
+$20,800/呎
 (26年-08月-24日)</t>
         </is>
       </c>
@@ -30826,17 +30826,17 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 813呎 (2房)
+          <t>C | 890呎 (2房)
 $1860万
-$22,879/呎
+$20,900/呎
 (26年-10月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 812呎 (2房)
+          <t>D | 892呎 (2房)
 $1846万
-$22,739/呎
+$20,700/呎
 (26年-09月-04日)</t>
         </is>
       </c>
@@ -30974,9 +30974,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 1595呎 (4+房)
+          <t>C | 1690呎 (4+房)
 $4779万
-$29,964/呎
+$28,280/呎
 (25年-01月-28日)</t>
         </is>
       </c>
@@ -30985,45 +30985,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20&amp;21</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 3007呎 (4+房)
+$9870万
+$32,823/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>20&amp;21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 878呎 (2房)
+$1924万
+$21,913/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 887呎 (2房)
+$1934万
+$21,800/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31034,25 +31034,25 @@
       <c r="B8" s="20" t="inlineStr"/>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1364呎 (3房)
 $3021万
-$23,902/呎
+$22,150/呎
 (25年-10月-08日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1912万
-$23,663/呎
+$21,777/呎
 (24年-03月-22日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1916万
-$23,712/呎
+$21,600/呎
 (24年-01月-12日)</t>
         </is>
       </c>
@@ -31065,9 +31065,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 2258呎 (4+房)
+          <t>A | 2376呎 (4+房)
 $7128万
-$31,568/呎
+$30,000/呎
 (26年-01月-27日)</t>
         </is>
       </c>
@@ -31083,33 +31083,33 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $3067万
-$24,230/呎
+$22,100/呎
 (26年-04月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $3043万
-$24,074/呎
+$22,050/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1883万
-$23,308/呎
+$21,450/呎
 (23年-12月-12日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1903万
-$23,547/呎
+$21,450/呎
 (24年-01月-18日)</t>
         </is>
       </c>
@@ -31122,17 +31122,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2983万
-$23,562/呎
+$21,491/呎
 (24年-03月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2891万
-$22,873/呎
+$20,950/呎
 (26年-06月-02日)</t>
         </is>
       </c>
@@ -31161,17 +31161,17 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2805万
-$22,158/呎
+$20,210/呎
 (26年-01月-26日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2789万
-$22,065/呎
+$20,210/呎
 (26年-01月-30日)</t>
         </is>
       </c>
@@ -31200,17 +31200,17 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2832万
-$22,366/呎
+$20,400/呎
 (26年-03月-31日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2815万
-$22,272/呎
+$20,400/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -31239,17 +31239,17 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2804万
-$22,147/呎
+$20,200/呎
 (26年-02月-04日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2815万
-$22,272/呎
+$20,400/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -31278,33 +31278,33 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2755万
-$21,763/呎
+$19,850/呎
 (26年-01月-26日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2726万
-$21,562/呎
+$19,750/呎
 (26年-01月-30日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1757万
-$21,741/呎
+$20,008/呎
 (23年-10月-12日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1775万
-$21,964/呎
+$20,008/呎
 (23年-10月-12日)</t>
         </is>
       </c>
@@ -31317,9 +31317,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2720万
-$21,489/呎
+$19,600/呎
 (26年-01月-06日)</t>
         </is>
       </c>
@@ -31341,9 +31341,9 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1756万
-$21,738/呎
+$19,802/呎
 (23年-10月-20日)</t>
         </is>
       </c>
@@ -31356,9 +31356,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2885万
-$22,791/呎
+$20,788/呎
 (24年-04月-02日)</t>
         </is>
       </c>
@@ -31395,17 +31395,17 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2679万
-$21,160/呎
+$19,300/呎
 (25年-04月-11日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2663万
-$21,071/呎
+$19,300/呎
 (25年-05月-09日)</t>
         </is>
       </c>
@@ -31419,9 +31419,9 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1774万
-$21,955/呎
+$20,000/呎
 (23年-12月-08日)</t>
         </is>
       </c>
@@ -31450,17 +31450,17 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1743万
-$21,570/呎
+$19,850/呎
 (23年-12月-11日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1761万
-$21,791/呎
+$19,850/呎
 (23年-12月-07日)</t>
         </is>
       </c>
@@ -31481,9 +31481,9 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2839万
-$22,462/呎
+$20,574/呎
 (23年-12月-04日)</t>
         </is>
       </c>
@@ -31520,25 +31520,25 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2677万
-$21,180/呎
+$19,400/呎
 (23年-11月-15日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1710万
-$21,168/呎
+$19,480/呎
 (23年-12月-19日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 808呎 (2房)
+          <t>D | 887呎 (2房)
 $1762万
-$21,803/呎
+$19,861/呎
 (23年-12月-04日)</t>
         </is>
       </c>
@@ -31551,25 +31551,25 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1266呎 (3房)
+          <t>A | 1388呎 (3房)
 $2741万
-$21,653/呎
+$19,750/呎
 (23年-12月-19日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2732万
-$21,617/呎
+$19,800/呎
 (24年-02月-08日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>C | 808呎 (2房)
+          <t>C | 878呎 (2房)
 $1677万
-$20,755/呎
+$19,100/呎
 (24年-03月-28日)</t>
         </is>
       </c>
@@ -31590,33 +31590,33 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1250呎 (3房)
+          <t>A | 1372呎 (3房)
 $2483万
-$19,866/呎
+$18,100/呎
 (25年-11月-11日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 1264呎 (3房)
+          <t>B | 1380呎 (3房)
 $2484万
-$19,652/呎
+$18,000/呎
 (25年-05月-20日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 753呎 (2房)
+          <t>C | 823呎 (2房)
 $1566万
-$20,797/呎
+$19,028/呎
 (24年-04月-10日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D | 753呎 (2房)
+          <t>D | 833呎 (2房)
 $1583万
-$21,019/呎
+$19,000/呎
 (24年-04月-15日)</t>
         </is>
       </c>
@@ -31747,9 +31747,9 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3236呎 (4+房)
+          <t>B | 3337呎 (4+房)
 $11446万
-$35,371/呎
+$34,300/呎
 (26年-03月-27日)</t>
         </is>
       </c>
@@ -31765,43 +31765,43 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1427呎 (3房)
+$3628万
+$25,423/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 848呎 (2房)
+$1849万
+$21,808/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2361呎 (4+房)
+$7508万
+$31,800/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31811,25 +31811,25 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3526万
-$26,694/呎
+$25,170/呎
 (26年-01月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3558万
-$26,551/呎
+$25,144/呎
 (26年-01月-19日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1833万
-$23,350/呎
+$21,616/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -31842,25 +31842,25 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3484万
-$26,376/呎
+$24,870/呎
 (26年-01月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3139万
-$23,428/呎
+$22,186/呎
 (26年-05月-22日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1798万
-$22,911/呎
+$21,209/呎
 (24年-05月-07日)</t>
         </is>
       </c>
@@ -31873,25 +31873,25 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3334万
-$25,241/呎
+$23,800/呎
 (26年-08月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3325万
-$24,815/呎
+$23,500/呎
 (26年-09月-17日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1778万
-$22,644/呎
+$20,962/呎
 (24年-04月-18日)</t>
         </is>
       </c>
@@ -31904,25 +31904,25 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3115万
-$23,584/呎
+$22,237/呎
 (26年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3136万
-$23,400/呎
+$22,160/呎
 (26年-05月-20日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1754万
-$22,340/呎
+$20,680/呎
 (24年-04月-12日)</t>
         </is>
       </c>
@@ -31935,25 +31935,25 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3110万
-$23,544/呎
+$22,200/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3640万
-$27,164/呎
+$25,724/呎
 (26年-09月-21日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1618万
-$20,611/呎
+$19,080/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -31966,25 +31966,25 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3082万
-$23,332/呎
+$22,000/呎
 (26年-08月-19日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3232万
-$24,118/呎
+$22,840/呎
 (26年-09月-18日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1598万
-$20,357/呎
+$18,844/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -31997,25 +31997,25 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3050万
-$23,089/呎
+$21,770/呎
 (26年-05月-28日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3198万
-$23,865/呎
+$22,600/呎
 (26年-09月-18日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1569万
-$19,985/呎
+$18,500/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -32028,25 +32028,25 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3030万
-$22,940/呎
+$21,630/呎
 (26年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3030万
-$22,612/呎
+$21,413/呎
 (26年-06月-26日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1567万
-$19,963/呎
+$18,480/呎
 (25年-12月-16日)</t>
         </is>
       </c>
@@ -32059,25 +32059,25 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3512万
-$26,588/呎
+$25,070/呎
 (26年-08月-10日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3141万
-$23,443/呎
+$22,200/呎
 (26年-08月-10日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1543万
-$19,661/呎
+$18,200/呎
 (25年-08月-20日)</t>
         </is>
       </c>
@@ -32090,25 +32090,25 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $2988万
-$22,621/呎
+$21,330/呎
 (26年-06月-04日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $2990万
-$22,313/呎
+$21,130/呎
 (26年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1539万
-$19,607/呎
+$18,150/呎
 (26年-03月-04日)</t>
         </is>
       </c>
@@ -32121,25 +32121,25 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $3068万
-$23,226/呎
+$21,900/呎
 (26年-06月-26日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3106万
-$23,179/呎
+$21,950/呎
 (26年-09月-28日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1526万
-$19,445/呎
+$18,000/呎
 (26年-01月-08日)</t>
         </is>
       </c>
@@ -32152,17 +32152,17 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $2921万
-$22,113/呎
+$20,850/呎
 (26年-05月-08日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1340呎 (3房)
+          <t>B | 1415呎 (3房)
 $3085万
-$23,020/呎
+$21,800/呎
 (26年-10月-13日)</t>
         </is>
       </c>
@@ -32183,9 +32183,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1321呎 (3房)
+          <t>A | 1401呎 (3房)
 $2928万
-$22,166/呎
+$20,900/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -32199,9 +32199,9 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1509万
-$19,229/呎
+$17,800/呎
 (26年-01月-19日)</t>
         </is>
       </c>
@@ -32230,9 +32230,9 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1503万
-$19,142/呎
+$17,720/呎
 (26年-02月-04日)</t>
         </is>
       </c>
